--- a/curriculum_videos.xlsx
+++ b/curriculum_videos.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruhathee\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D373CDF5-DE57-4444-8EA0-2297231C214D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="15600" windowHeight="11760" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="CM" sheetId="1" r:id="rId1"/>
@@ -19,10 +13,11 @@
     <sheet name="APT" sheetId="2" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
     <sheet name="APT HW" sheetId="4" r:id="rId6"/>
+    <sheet name="APT_Notes" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="124519"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="365">
   <si>
     <t>CL72</t>
   </si>
@@ -1128,13 +1123,19 @@
   </si>
   <si>
     <t>https://github.com/nalinis07/APT_Class_Copy_Links/blob/MASTER/APT_Lesson_88_Class_Copy.ipynb</t>
+  </si>
+  <si>
+    <t>https://s3-student-datasets-bucket.whjr.online/images/sst2.png</t>
+  </si>
+  <si>
+    <t>Images location in colab try this if not displayed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1161,6 +1162,12 @@
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="21"/>
+      <color rgb="FF0000FF"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1226,7 +1233,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1266,6 +1273,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1327,7 +1335,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1362,7 +1370,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1539,18 +1547,18 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A4:B40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1558,7 +1566,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -1566,7 +1574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1574,7 +1582,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1582,12 +1590,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1595,12 +1603,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="B10" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1608,12 +1616,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="B12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1621,12 +1629,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="B15" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1634,12 +1642,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="B18" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -1647,7 +1655,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -1655,7 +1663,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>46</v>
       </c>
@@ -1663,12 +1671,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2">
       <c r="B26" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>49</v>
       </c>
@@ -1676,7 +1684,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -1684,7 +1692,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>75</v>
       </c>
@@ -1692,7 +1700,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>88</v>
       </c>
@@ -1700,7 +1708,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
         <v>89</v>
       </c>
@@ -1708,12 +1716,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>102</v>
       </c>
@@ -1723,41 +1731,41 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B5" r:id="rId1" xr:uid="{8C1701C3-F8A2-4CC1-9A3B-559DB17F0B4F}"/>
-    <hyperlink ref="B4" r:id="rId2" xr:uid="{FED23F09-87A8-410D-A876-DFD0A73ABA26}"/>
-    <hyperlink ref="B7" r:id="rId3" xr:uid="{DC496038-3041-4DC7-845F-23D863B34770}"/>
-    <hyperlink ref="B9" r:id="rId4" xr:uid="{22590378-B2C0-43C6-AEAD-9CD349A57C7E}"/>
-    <hyperlink ref="B10" r:id="rId5" xr:uid="{A41420D4-6C8B-43D5-A163-61E11CD3C7A0}"/>
-    <hyperlink ref="B14" r:id="rId6" xr:uid="{98CEFE64-1D77-444F-ACF3-29185701876E}"/>
-    <hyperlink ref="B17" r:id="rId7" xr:uid="{170E0CDC-C237-4913-B245-BF4AC2E9989A}"/>
-    <hyperlink ref="B18" r:id="rId8" xr:uid="{F672ACD9-1EAF-4F35-8DE8-ADD5DE499F7B}"/>
-    <hyperlink ref="B21" r:id="rId9" xr:uid="{19A7655D-DA8F-4548-B468-8447D1C711E9}"/>
-    <hyperlink ref="B25" r:id="rId10" xr:uid="{BDE6C9E6-1A40-483F-A15B-2E91EBA93281}"/>
+    <hyperlink ref="B5" r:id="rId1"/>
+    <hyperlink ref="B4" r:id="rId2"/>
+    <hyperlink ref="B7" r:id="rId3"/>
+    <hyperlink ref="B9" r:id="rId4"/>
+    <hyperlink ref="B10" r:id="rId5"/>
+    <hyperlink ref="B14" r:id="rId6"/>
+    <hyperlink ref="B17" r:id="rId7"/>
+    <hyperlink ref="B18" r:id="rId8"/>
+    <hyperlink ref="B21" r:id="rId9"/>
+    <hyperlink ref="B25" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{686192AD-7868-465E-BA5D-875A0201E7EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="19.21875" customWidth="1"/>
-    <col min="4" max="4" width="41.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="41.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="D1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>118</v>
       </c>
@@ -1765,17 +1773,17 @@
         <v>199</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="C5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -1786,7 +1794,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>97</v>
       </c>
@@ -1797,7 +1805,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>344</v>
       </c>
@@ -1808,7 +1816,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>349</v>
       </c>
@@ -1819,7 +1827,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1830,12 +1838,12 @@
         <v>356</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="D21" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>13</v>
       </c>
@@ -1848,20 +1856,20 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D22" r:id="rId1" xr:uid="{C9AF7FF0-9DDA-4F67-8BD0-2B0C37D6E1AD}"/>
-    <hyperlink ref="D20" r:id="rId2" xr:uid="{6C0A2F1E-CDF0-475D-B768-5CFBA6306C33}"/>
-    <hyperlink ref="D18" r:id="rId3" xr:uid="{272BF3EC-0DD3-4ABE-90C2-CCAC31E34C80}"/>
+    <hyperlink ref="D22" r:id="rId1"/>
+    <hyperlink ref="D20" r:id="rId2"/>
+    <hyperlink ref="D18" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{114F7649-DC29-4C5A-9795-439D74C05CEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>345</v>
       </c>
@@ -1871,30 +1879,30 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" xr:uid="{8F023EDA-2D5D-4A9F-9672-84AD96C29081}"/>
-    <hyperlink ref="D1" r:id="rId2" xr:uid="{55E661A2-9A3B-4426-9674-937625C06169}"/>
+    <hyperlink ref="A1" r:id="rId1"/>
+    <hyperlink ref="D1" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA831A98-00F9-4D7E-BF48-CF6838CBF5E9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P229"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="8.85546875" style="2"/>
     <col min="2" max="2" width="36" style="2" customWidth="1"/>
     <col min="3" max="5" width="0" style="2" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="51.33203125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="48.88671875" style="2" customWidth="1"/>
-    <col min="8" max="14" width="8.88671875" style="2" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="51.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="48.85546875" style="2" customWidth="1"/>
+    <col min="8" max="14" width="8.85546875" style="2" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="33" style="2" customWidth="1"/>
-    <col min="16" max="16" width="42.21875" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="8.88671875" style="2"/>
+    <col min="16" max="16" width="42.28515625" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="4" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>141</v>
       </c>
@@ -1914,7 +1922,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="30">
       <c r="A2" s="2" t="s">
         <v>72</v>
       </c>
@@ -1925,7 +1933,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="30">
       <c r="A3" s="2" t="s">
         <v>85</v>
       </c>
@@ -1933,7 +1941,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="30">
       <c r="A4" s="2" t="s">
         <v>56</v>
       </c>
@@ -1944,7 +1952,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:16" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" s="9" customFormat="1" ht="30">
       <c r="A5" s="9" t="s">
         <v>54</v>
       </c>
@@ -1955,7 +1963,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:16" s="10" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" s="10" customFormat="1" ht="30">
       <c r="A6" s="10" t="s">
         <v>63</v>
       </c>
@@ -1966,7 +1974,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:16" s="10" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" s="10" customFormat="1" ht="30.75" thickBot="1">
       <c r="A7" s="10" t="s">
         <v>81</v>
       </c>
@@ -1975,21 +1983,21 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:16" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" s="13" customFormat="1" ht="30.75" thickBot="1">
       <c r="A8" s="12" t="s">
         <v>105</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="14" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" ht="15.75" thickBot="1">
       <c r="B9" s="5"/>
     </row>
-    <row r="10" spans="1:16" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
       <c r="A10" s="12" t="s">
         <v>137</v>
       </c>
@@ -2007,10 +2015,10 @@
         <v>139</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" ht="15.75" thickBot="1">
       <c r="B11" s="5"/>
     </row>
-    <row r="12" spans="1:16" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
       <c r="A12" s="12" t="s">
         <v>152</v>
       </c>
@@ -2028,10 +2036,10 @@
         <v>155</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" ht="15.75" thickBot="1">
       <c r="B13" s="5"/>
     </row>
-    <row r="14" spans="1:16" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
       <c r="A14" s="12" t="s">
         <v>160</v>
       </c>
@@ -2049,10 +2057,10 @@
         <v>155</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" ht="15.75" thickBot="1">
       <c r="B15" s="5"/>
     </row>
-    <row r="16" spans="1:16" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
       <c r="A16" s="12" t="s">
         <v>29</v>
       </c>
@@ -2072,12 +2080,12 @@
         <v>155</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" ht="30.75" thickBot="1">
       <c r="F17" s="2" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="18" spans="1:16" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
       <c r="A18" s="12" t="s">
         <v>172</v>
       </c>
@@ -2094,8 +2102,8 @@
         <v>155</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:16" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="20" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
       <c r="A20" s="12" t="s">
         <v>174</v>
       </c>
@@ -2112,8 +2120,8 @@
         <v>155</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="1:16" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="22" spans="1:16" s="13" customFormat="1" ht="30.75" thickBot="1">
       <c r="A22" s="12" t="s">
         <v>0</v>
       </c>
@@ -2127,8 +2135,8 @@
         <v>176</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="1:16" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="24" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
       <c r="A24" s="12" t="s">
         <v>4</v>
       </c>
@@ -2148,8 +2156,8 @@
         <v>203</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="1:16" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="26" spans="1:16" s="13" customFormat="1" ht="30.75" thickBot="1">
       <c r="A26" s="12" t="s">
         <v>114</v>
       </c>
@@ -2169,8 +2177,8 @@
         <v>192</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="1:16" s="13" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="28" spans="1:16" s="13" customFormat="1" ht="27.6" customHeight="1" thickBot="1">
       <c r="A28" s="12" t="s">
         <v>116</v>
       </c>
@@ -2190,8 +2198,8 @@
         <v>192</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="1:16" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="30" spans="1:16" s="13" customFormat="1" ht="30.75" thickBot="1">
       <c r="A30" s="12" t="s">
         <v>17</v>
       </c>
@@ -2208,8 +2216,8 @@
         <v>192</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="1:16" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="32" spans="1:16" s="13" customFormat="1" ht="30.75" thickBot="1">
       <c r="A32" s="12" t="s">
         <v>179</v>
       </c>
@@ -2226,7 +2234,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2">
       <c r="A34" s="2" t="s">
         <v>60</v>
       </c>
@@ -2234,12 +2242,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" ht="45">
       <c r="B35" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2">
       <c r="A36" s="2" t="s">
         <v>108</v>
       </c>
@@ -2247,7 +2255,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2">
       <c r="A37" s="2" t="s">
         <v>117</v>
       </c>
@@ -2255,7 +2263,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2">
       <c r="A38" s="2" t="s">
         <v>10</v>
       </c>
@@ -2263,12 +2271,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2">
       <c r="B39" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2">
       <c r="A40" s="2" t="s">
         <v>13</v>
       </c>
@@ -2276,17 +2284,17 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2">
       <c r="B41" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2">
       <c r="A42" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2">
       <c r="A44" s="2" t="s">
         <v>22</v>
       </c>
@@ -2294,12 +2302,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2">
       <c r="B45" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2">
       <c r="A47" s="2" t="s">
         <v>33</v>
       </c>
@@ -2307,12 +2315,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2">
       <c r="B48" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5">
       <c r="A50" s="2" t="s">
         <v>36</v>
       </c>
@@ -2320,27 +2328,27 @@
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5">
       <c r="B51" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5">
       <c r="A52" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5">
       <c r="B53" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5">
       <c r="B54" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" ht="150">
       <c r="A56" s="2">
         <v>132</v>
       </c>
@@ -2351,7 +2359,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" ht="180">
       <c r="A58" s="2">
         <v>133</v>
       </c>
@@ -2362,12 +2370,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" ht="90">
       <c r="E59" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" ht="180">
       <c r="A60" s="2">
         <v>134</v>
       </c>
@@ -2378,12 +2386,12 @@
         <v>68</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" ht="90">
       <c r="E61" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" ht="180">
       <c r="A63" s="2">
         <v>135</v>
       </c>
@@ -2391,7 +2399,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" ht="180">
       <c r="A65" s="2">
         <v>136</v>
       </c>
@@ -2399,7 +2407,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" ht="180">
       <c r="A67" s="2">
         <v>137</v>
       </c>
@@ -2407,7 +2415,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" ht="180">
       <c r="A69" s="2">
         <v>138</v>
       </c>
@@ -2421,12 +2429,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="70" spans="1:16" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" ht="165">
       <c r="E70" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="71" spans="1:16" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" ht="180">
       <c r="A71" s="2">
         <v>139</v>
       </c>
@@ -2440,7 +2448,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="73" spans="1:16" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" ht="180">
       <c r="A73" s="2">
         <v>140</v>
       </c>
@@ -2454,7 +2462,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="74" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" ht="45">
       <c r="O74" s="2" t="s">
         <v>134</v>
       </c>
@@ -2462,7 +2470,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="75" spans="1:16" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" ht="180">
       <c r="A75" s="2">
         <v>141</v>
       </c>
@@ -2473,7 +2481,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="77" spans="1:16" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" ht="180">
       <c r="A77" s="2">
         <v>142</v>
       </c>
@@ -2484,7 +2492,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="79" spans="1:16" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" ht="180">
       <c r="A79" s="2">
         <v>143</v>
       </c>
@@ -2495,17 +2503,17 @@
         <v>124</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16">
       <c r="P80" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="81" spans="1:16" ht="88.8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" ht="90">
       <c r="P81" s="8" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="82" spans="1:16" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" ht="195">
       <c r="A82" s="2">
         <v>144</v>
       </c>
@@ -2516,12 +2524,12 @@
         <v>123</v>
       </c>
     </row>
-    <row r="83" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" ht="30">
       <c r="P83" s="6" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" ht="30">
       <c r="A88" s="2">
         <v>78</v>
       </c>
@@ -2535,13 +2543,13 @@
         <v>192</v>
       </c>
     </row>
-    <row r="89" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" ht="30">
       <c r="G89" s="5" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="90" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="91" spans="1:16" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="91" spans="1:16" ht="45.75" thickBot="1">
       <c r="A91" s="2">
         <v>79</v>
       </c>
@@ -2558,7 +2566,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="93" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" ht="45">
       <c r="A93" s="2">
         <v>80</v>
       </c>
@@ -2575,7 +2583,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="95" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" ht="45">
       <c r="A95" s="2">
         <v>81</v>
       </c>
@@ -2592,7 +2600,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="97" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" ht="45">
       <c r="A97" s="2">
         <v>82</v>
       </c>
@@ -2609,7 +2617,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="99" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" ht="45">
       <c r="A99" s="2">
         <v>83</v>
       </c>
@@ -2626,7 +2634,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="101" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" ht="45">
       <c r="A101" s="2">
         <v>84</v>
       </c>
@@ -2643,7 +2651,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" ht="45">
       <c r="A103" s="2">
         <v>85</v>
       </c>
@@ -2660,7 +2668,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" ht="45">
       <c r="A105" s="2">
         <v>86</v>
       </c>
@@ -2677,7 +2685,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" ht="36" customHeight="1">
       <c r="O106" s="2" t="s">
         <v>225</v>
       </c>
@@ -2685,7 +2693,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" ht="45">
       <c r="A107" s="2">
         <v>87</v>
       </c>
@@ -2702,7 +2710,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" ht="45">
       <c r="O108" s="2" t="s">
         <v>225</v>
       </c>
@@ -2710,7 +2718,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" ht="45">
       <c r="A110" s="2">
         <v>88</v>
       </c>
@@ -2727,7 +2735,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="112" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" ht="45">
       <c r="A112" s="2">
         <v>89</v>
       </c>
@@ -2741,7 +2749,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="114" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:16" ht="45">
       <c r="A114" s="2">
         <v>90</v>
       </c>
@@ -2755,7 +2763,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="116" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" ht="30">
       <c r="A116" s="2">
         <v>91</v>
       </c>
@@ -2766,7 +2774,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="118" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" ht="45">
       <c r="A118" s="2">
         <v>92</v>
       </c>
@@ -2780,7 +2788,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="120" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:16" ht="45">
       <c r="A120" s="2">
         <v>93</v>
       </c>
@@ -2794,7 +2802,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="122" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:16" ht="45">
       <c r="A122" s="2">
         <v>94</v>
       </c>
@@ -2808,7 +2816,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="124" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:16" ht="45">
       <c r="A124" s="2">
         <v>95</v>
       </c>
@@ -2822,7 +2830,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="126" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:16" ht="45">
       <c r="A126" s="2">
         <v>96</v>
       </c>
@@ -2836,8 +2844,8 @@
         <v>218</v>
       </c>
     </row>
-    <row r="127" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="128" spans="1:16" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="128" spans="1:16" ht="45.75" thickBot="1">
       <c r="A128" s="2">
         <v>97</v>
       </c>
@@ -2851,7 +2859,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="130" spans="1:16" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:16" ht="25.15" customHeight="1">
       <c r="A130" s="2">
         <v>98</v>
       </c>
@@ -2865,7 +2873,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="132" spans="1:16" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:16" ht="29.45" customHeight="1">
       <c r="A132" s="2">
         <v>99</v>
       </c>
@@ -2879,7 +2887,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="134" spans="1:16" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:16" ht="33.6" customHeight="1">
       <c r="A134" s="2">
         <v>100</v>
       </c>
@@ -2893,7 +2901,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="136" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:16" ht="45">
       <c r="A136" s="2">
         <v>101</v>
       </c>
@@ -2907,7 +2915,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="138" spans="1:16" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:16" ht="27" customHeight="1">
       <c r="A138" s="2">
         <v>102</v>
       </c>
@@ -2921,7 +2929,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="140" spans="1:16" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:16" ht="32.450000000000003" customHeight="1">
       <c r="A140" s="2">
         <v>103</v>
       </c>
@@ -2932,7 +2940,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="142" spans="1:16" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:16" ht="27" customHeight="1">
       <c r="A142" s="2">
         <v>104</v>
       </c>
@@ -2943,7 +2951,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="144" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:16" ht="27.6" customHeight="1">
       <c r="A144" s="2">
         <v>105</v>
       </c>
@@ -2957,7 +2965,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="146" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:16" ht="27.6" customHeight="1">
       <c r="A146" s="2">
         <v>106</v>
       </c>
@@ -2971,7 +2979,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="148" spans="1:16" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:16" ht="34.15" customHeight="1">
       <c r="A148" s="2">
         <v>107</v>
       </c>
@@ -2985,7 +2993,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="150" spans="1:16" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:16" ht="35.450000000000003" customHeight="1">
       <c r="A150" s="2">
         <v>108</v>
       </c>
@@ -2999,7 +3007,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="152" spans="1:16" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:16" ht="30.6" customHeight="1">
       <c r="A152" s="2">
         <v>109</v>
       </c>
@@ -3013,7 +3021,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="153" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:16" ht="45">
       <c r="O153" s="2" t="s">
         <v>263</v>
       </c>
@@ -3021,7 +3029,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="155" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:16" ht="36" customHeight="1">
       <c r="A155" s="2">
         <v>110</v>
       </c>
@@ -3035,7 +3043,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="157" spans="1:16" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:16" ht="25.15" customHeight="1">
       <c r="A157" s="2">
         <v>111</v>
       </c>
@@ -3049,7 +3057,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="159" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:16" ht="30" customHeight="1">
       <c r="A159" s="2">
         <v>112</v>
       </c>
@@ -3063,7 +3071,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="161" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:16" ht="24" customHeight="1">
       <c r="A161" s="2">
         <v>113</v>
       </c>
@@ -3077,7 +3085,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="163" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:16" ht="45">
       <c r="A163" s="2">
         <v>114</v>
       </c>
@@ -3091,7 +3099,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="165" spans="1:16" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:16" ht="34.15" customHeight="1">
       <c r="A165" s="2">
         <v>115</v>
       </c>
@@ -3105,7 +3113,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="167" spans="1:16" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:16" ht="25.9" customHeight="1">
       <c r="A167" s="2">
         <v>116</v>
       </c>
@@ -3119,7 +3127,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="169" spans="1:16" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:16" ht="37.9" customHeight="1">
       <c r="A169" s="2">
         <v>117</v>
       </c>
@@ -3133,7 +3141,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="171" spans="1:16" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:16" ht="37.15" customHeight="1">
       <c r="A171" s="2">
         <v>118</v>
       </c>
@@ -3147,7 +3155,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="173" spans="1:16" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:16" ht="28.15" customHeight="1">
       <c r="A173" s="2">
         <v>119</v>
       </c>
@@ -3161,7 +3169,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="175" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:16" ht="39" customHeight="1">
       <c r="A175" s="2">
         <v>120</v>
       </c>
@@ -3175,7 +3183,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="177" spans="1:16" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:16" ht="31.15" customHeight="1">
       <c r="A177" s="2">
         <v>121</v>
       </c>
@@ -3189,7 +3197,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="179" spans="1:16" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:16" ht="34.9" customHeight="1">
       <c r="A179" s="2">
         <v>122</v>
       </c>
@@ -3203,7 +3211,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="181" spans="1:16" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:16" ht="25.15" customHeight="1">
       <c r="A181" s="2">
         <v>123</v>
       </c>
@@ -3217,7 +3225,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="183" spans="1:16" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:16" ht="50.45" customHeight="1">
       <c r="A183" s="2">
         <v>124</v>
       </c>
@@ -3231,8 +3239,8 @@
         <v>291</v>
       </c>
     </row>
-    <row r="184" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="185" spans="1:16" ht="46.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="185" spans="1:16" ht="46.9" customHeight="1" thickBot="1">
       <c r="A185" s="2">
         <v>125</v>
       </c>
@@ -3246,8 +3254,8 @@
         <v>203</v>
       </c>
     </row>
-    <row r="186" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="187" spans="1:16" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="187" spans="1:16" ht="58.15" customHeight="1" thickBot="1">
       <c r="A187" s="2">
         <v>126</v>
       </c>
@@ -3261,7 +3269,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="188" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:16" ht="45">
       <c r="O188" s="2" t="s">
         <v>297</v>
       </c>
@@ -3269,7 +3277,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="190" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:16" ht="33" customHeight="1">
       <c r="A190" s="2">
         <v>127</v>
       </c>
@@ -3283,7 +3291,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="193" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:16" ht="33" customHeight="1">
       <c r="A193" s="2">
         <v>128</v>
       </c>
@@ -3294,7 +3302,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="195" spans="1:16" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:16" ht="46.15" customHeight="1">
       <c r="A195" s="2">
         <v>129</v>
       </c>
@@ -3305,7 +3313,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="197" spans="1:16" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:16" ht="31.15" customHeight="1">
       <c r="A197" s="2">
         <v>130</v>
       </c>
@@ -3319,7 +3327,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="199" spans="1:16" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:16" ht="37.9" customHeight="1">
       <c r="A199" s="2">
         <v>131</v>
       </c>
@@ -3333,7 +3341,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="201" spans="1:16" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:16" ht="28.15" customHeight="1">
       <c r="A201" s="2">
         <v>132</v>
       </c>
@@ -3347,7 +3355,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="203" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:16" ht="24" customHeight="1">
       <c r="A203" s="2">
         <v>133</v>
       </c>
@@ -3361,8 +3369,8 @@
         <v>308</v>
       </c>
     </row>
-    <row r="204" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="205" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:16" ht="23.45" customHeight="1"/>
+    <row r="205" spans="1:16" ht="42" customHeight="1">
       <c r="A205" s="2">
         <v>134</v>
       </c>
@@ -3376,7 +3384,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="207" spans="1:16" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:16" ht="65.45" customHeight="1">
       <c r="A207" s="2">
         <v>135</v>
       </c>
@@ -3390,7 +3398,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="208" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:16" ht="45">
       <c r="O208" s="2" t="s">
         <v>313</v>
       </c>
@@ -3398,7 +3406,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="210" spans="1:16" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:16" ht="40.15" customHeight="1">
       <c r="O210" s="2" t="s">
         <v>315</v>
       </c>
@@ -3406,7 +3414,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="211" spans="1:16" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:16" ht="28.15" customHeight="1">
       <c r="A211" s="2">
         <v>136</v>
       </c>
@@ -3420,7 +3428,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="213" spans="1:16" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:16" ht="46.9" customHeight="1">
       <c r="A213" s="2">
         <v>137</v>
       </c>
@@ -3434,7 +3442,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="215" spans="1:16" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:16" ht="46.9" customHeight="1">
       <c r="A215" s="2">
         <v>138</v>
       </c>
@@ -3448,7 +3456,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="217" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:16" ht="33" customHeight="1">
       <c r="A217" s="2">
         <v>139</v>
       </c>
@@ -3462,7 +3470,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="219" spans="1:16" ht="63.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:16" ht="63.6" customHeight="1">
       <c r="A219" s="2">
         <v>140</v>
       </c>
@@ -3476,7 +3484,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="220" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:16" ht="45">
       <c r="O220" s="2" t="s">
         <v>329</v>
       </c>
@@ -3484,7 +3492,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="222" spans="1:16" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:16" ht="48.6" customHeight="1">
       <c r="A222" s="2">
         <v>141</v>
       </c>
@@ -3495,7 +3503,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="224" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:16" ht="45" customHeight="1">
       <c r="A224" s="2">
         <v>142</v>
       </c>
@@ -3509,12 +3517,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:16" ht="30">
       <c r="P225" s="2" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="226" spans="1:16" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:16" ht="39.6" customHeight="1">
       <c r="A226" s="2">
         <v>143</v>
       </c>
@@ -3528,12 +3536,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:16" ht="30">
       <c r="P227" s="2" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="228" spans="1:16" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:16" ht="52.9" customHeight="1">
       <c r="A228" s="2">
         <v>144</v>
       </c>
@@ -3544,88 +3552,89 @@
         <v>123</v>
       </c>
     </row>
-    <row r="229" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:16" ht="30">
       <c r="P229" s="6" t="s">
         <v>122</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B41" r:id="rId1" xr:uid="{C97A4869-59AA-46DC-A7EB-888A4016ED42}"/>
-    <hyperlink ref="B50" r:id="rId2" xr:uid="{4D31F09B-134A-40C2-8E08-46EEA1C2D3DC}"/>
-    <hyperlink ref="B53" r:id="rId3" xr:uid="{5809508D-AA60-4F6F-943C-8674D4B69EAB}"/>
-    <hyperlink ref="B56" r:id="rId4" xr:uid="{E7D7A160-8848-4D18-8FBF-5DE4B6BFE7AD}"/>
-    <hyperlink ref="B6" r:id="rId5" xr:uid="{DDA8829C-6B0A-42D9-8893-5EBE2B274522}"/>
-    <hyperlink ref="E71" r:id="rId6" xr:uid="{8C7CA2AB-2375-4612-A049-6B82A36C7742}"/>
-    <hyperlink ref="B36" r:id="rId7" xr:uid="{CCE4692B-3908-4B2A-BD5A-5E0AD4D33C9B}"/>
-    <hyperlink ref="E69" r:id="rId8" xr:uid="{9D6AD111-1777-4DE0-B172-E08524AC9A59}"/>
-    <hyperlink ref="P83" r:id="rId9" xr:uid="{3E1ABDE5-9CCE-4B1E-89FC-6E9CA4F68AE4}"/>
-    <hyperlink ref="P82" r:id="rId10" xr:uid="{C5DC49FB-BEEC-4023-9058-C7B7E1C7E096}"/>
-    <hyperlink ref="P73" r:id="rId11" xr:uid="{D03427DA-CF02-4EF6-8B8F-943CBB4FCB74}"/>
-    <hyperlink ref="P69" r:id="rId12" xr:uid="{1D715420-7DC1-41D3-8429-C94320C187FE}"/>
-    <hyperlink ref="G26" r:id="rId13" xr:uid="{5B7FCA62-3B55-489F-86CB-FD7BE9F2D384}"/>
-    <hyperlink ref="G10" r:id="rId14" xr:uid="{14D1C84E-6C0B-4BF9-8A7E-4D02F91D4C06}"/>
-    <hyperlink ref="F18" r:id="rId15" xr:uid="{3051E7A2-6818-47A8-9FBD-3CAC5C77AFC5}"/>
-    <hyperlink ref="F20" r:id="rId16" xr:uid="{8A836FD3-125C-41BE-83D1-F4C7271B8B00}"/>
-    <hyperlink ref="F24" r:id="rId17" xr:uid="{DFD68178-47E2-4FFC-8C31-E8C43A14880E}"/>
-    <hyperlink ref="F26" r:id="rId18" xr:uid="{9AABDCFE-942F-4E05-971A-D57E31C4E1E9}"/>
-    <hyperlink ref="F28" r:id="rId19" xr:uid="{785626F7-0A27-4BFC-8B79-8B35BA69B9C6}"/>
-    <hyperlink ref="F30" r:id="rId20" xr:uid="{8B9E5BC7-9F41-4AB5-A4E7-DBF3B8D4C5A2}"/>
-    <hyperlink ref="F32" r:id="rId21" xr:uid="{23484AC0-227A-44D7-A9E9-C4CF7D2653D2}"/>
-    <hyperlink ref="P24" r:id="rId22" xr:uid="{4F848DAC-66E7-4262-9C1D-E1AF9A47BB2D}"/>
-    <hyperlink ref="G22" r:id="rId23" xr:uid="{D2F4E687-0465-4D63-B9E8-B67C92615136}"/>
-    <hyperlink ref="G12" r:id="rId24" xr:uid="{4593D63B-3C76-4E0B-9F9D-3C830B9672FF}"/>
-    <hyperlink ref="G28" r:id="rId25" xr:uid="{C48E5118-24A2-4EB8-948F-61FBB3EFB6A6}"/>
-    <hyperlink ref="G30" r:id="rId26" xr:uid="{230B9C07-A0B8-4FC2-84D8-4E0197501E2A}"/>
-    <hyperlink ref="F91" r:id="rId27" xr:uid="{370A4F36-26E0-4C1E-BEBD-AE774765184A}"/>
-    <hyperlink ref="P91" r:id="rId28" xr:uid="{DE2F0116-4563-4236-AEB3-AB5231469930}"/>
-    <hyperlink ref="G88" r:id="rId29" xr:uid="{47244D19-27C2-46FB-B326-EA750834365C}"/>
-    <hyperlink ref="G101" r:id="rId30" xr:uid="{414F041A-4CD5-49AE-BBD9-68B3807E1025}"/>
-    <hyperlink ref="G103" r:id="rId31" xr:uid="{8D106B85-1AF4-4516-AD94-383001ADF4E0}"/>
-    <hyperlink ref="G105" r:id="rId32" xr:uid="{C2E6FBB8-724A-440B-966B-BB0A0DC85B75}"/>
-    <hyperlink ref="F163" r:id="rId33" xr:uid="{DDC17788-DE7E-4621-9538-D90DE7B7A969}"/>
-    <hyperlink ref="P185" r:id="rId34" xr:uid="{B80DC06F-03E8-4573-9001-D9B4C1DD6AFA}"/>
-    <hyperlink ref="P187" r:id="rId35" xr:uid="{197CA345-3C9C-4443-9A79-71D6B68586F3}"/>
-    <hyperlink ref="F205" r:id="rId36" xr:uid="{403F929D-6946-4914-97CC-432CB1F5087E}"/>
-    <hyperlink ref="F14" r:id="rId37" location="scrollTo=5f2emlnJM56A" xr:uid="{6CD6094D-3E4E-4E51-B94B-25611379B0E3}"/>
-    <hyperlink ref="F215" r:id="rId38" xr:uid="{6C4CC923-3674-4888-8A47-796B37DBAD48}"/>
-    <hyperlink ref="P79" r:id="rId39" xr:uid="{14C342B9-B02E-41BF-897B-8A9BF09C7A62}"/>
-    <hyperlink ref="P228" r:id="rId40" xr:uid="{30F8E4CF-EBF0-4808-9AC4-CF24C68F6BDA}"/>
-    <hyperlink ref="P229" r:id="rId41" xr:uid="{0D9AF039-F8FD-452C-A7C4-862EFAC66E44}"/>
-    <hyperlink ref="B28" r:id="rId42" xr:uid="{3B51182C-C2AF-4E76-B4FC-B30956087745}"/>
-    <hyperlink ref="F93" r:id="rId43" xr:uid="{7727788D-F5FE-45D9-A2AF-A26EE854AA01}"/>
-    <hyperlink ref="G93" r:id="rId44" xr:uid="{88ED669C-EE31-44B8-B08B-955010BDC58A}"/>
-    <hyperlink ref="F95" r:id="rId45" xr:uid="{FCCEFBA0-A9B4-4AEB-8D9F-3F351BA04B6D}"/>
-    <hyperlink ref="F118" r:id="rId46" xr:uid="{EC44383E-68B9-4FE0-A516-0F2BF2A5EAAF}"/>
-    <hyperlink ref="F134" r:id="rId47" xr:uid="{99F1AE22-EC2C-49C3-ABD2-DF61849F9DCA}"/>
-    <hyperlink ref="F97" r:id="rId48" xr:uid="{7E6A8825-1F7C-4C0C-A2F7-6D7ABC4250C2}"/>
-    <hyperlink ref="G97" r:id="rId49" xr:uid="{B6278EFF-162A-4C74-ABDA-BE0561549245}"/>
-    <hyperlink ref="G99" r:id="rId50" xr:uid="{163B433A-18D7-47D0-85C8-BC44D115F223}"/>
-    <hyperlink ref="F99" r:id="rId51" xr:uid="{E95845CA-BEC5-4052-B480-AD3B454DC7B5}"/>
-    <hyperlink ref="F101" r:id="rId52" xr:uid="{374A9DAB-3859-44DB-B986-8028FB9C2933}"/>
-    <hyperlink ref="F105" r:id="rId53" xr:uid="{11ADC725-B183-4783-B34A-196EA872B3BF}"/>
-    <hyperlink ref="F107" r:id="rId54" xr:uid="{119C8066-76E2-44F8-B195-E78F6EBDDCDD}"/>
-    <hyperlink ref="F110" r:id="rId55" xr:uid="{88A1DD6A-66B1-4C83-B0FD-AEB598D07C1C}"/>
-    <hyperlink ref="G110" r:id="rId56" xr:uid="{B4F4C830-3EFF-4AA8-BE56-AB1B9B764C77}"/>
-    <hyperlink ref="F112" r:id="rId57" xr:uid="{05C41C31-3125-4E68-9834-57AACF2AF6E4}"/>
+    <hyperlink ref="B41" r:id="rId1"/>
+    <hyperlink ref="B50" r:id="rId2"/>
+    <hyperlink ref="B53" r:id="rId3"/>
+    <hyperlink ref="B56" r:id="rId4"/>
+    <hyperlink ref="B6" r:id="rId5"/>
+    <hyperlink ref="E71" r:id="rId6"/>
+    <hyperlink ref="B36" r:id="rId7"/>
+    <hyperlink ref="E69" r:id="rId8"/>
+    <hyperlink ref="P83" r:id="rId9"/>
+    <hyperlink ref="P82" r:id="rId10"/>
+    <hyperlink ref="P73" r:id="rId11"/>
+    <hyperlink ref="P69" r:id="rId12"/>
+    <hyperlink ref="G26" r:id="rId13"/>
+    <hyperlink ref="G10" r:id="rId14"/>
+    <hyperlink ref="F18" r:id="rId15"/>
+    <hyperlink ref="F20" r:id="rId16"/>
+    <hyperlink ref="F24" r:id="rId17"/>
+    <hyperlink ref="F26" r:id="rId18"/>
+    <hyperlink ref="F28" r:id="rId19"/>
+    <hyperlink ref="F30" r:id="rId20"/>
+    <hyperlink ref="F32" r:id="rId21"/>
+    <hyperlink ref="P24" r:id="rId22"/>
+    <hyperlink ref="G22" r:id="rId23"/>
+    <hyperlink ref="G12" r:id="rId24"/>
+    <hyperlink ref="G28" r:id="rId25"/>
+    <hyperlink ref="G30" r:id="rId26"/>
+    <hyperlink ref="F91" r:id="rId27"/>
+    <hyperlink ref="P91" r:id="rId28"/>
+    <hyperlink ref="G88" r:id="rId29"/>
+    <hyperlink ref="G101" r:id="rId30"/>
+    <hyperlink ref="G103" r:id="rId31"/>
+    <hyperlink ref="G105" r:id="rId32"/>
+    <hyperlink ref="F163" r:id="rId33"/>
+    <hyperlink ref="P185" r:id="rId34"/>
+    <hyperlink ref="P187" r:id="rId35"/>
+    <hyperlink ref="F205" r:id="rId36"/>
+    <hyperlink ref="F14" r:id="rId37" location="scrollTo=5f2emlnJM56A"/>
+    <hyperlink ref="F215" r:id="rId38"/>
+    <hyperlink ref="P79" r:id="rId39"/>
+    <hyperlink ref="P228" r:id="rId40"/>
+    <hyperlink ref="P229" r:id="rId41"/>
+    <hyperlink ref="B28" r:id="rId42"/>
+    <hyperlink ref="F93" r:id="rId43"/>
+    <hyperlink ref="G93" r:id="rId44"/>
+    <hyperlink ref="F95" r:id="rId45"/>
+    <hyperlink ref="F118" r:id="rId46"/>
+    <hyperlink ref="F134" r:id="rId47"/>
+    <hyperlink ref="F97" r:id="rId48"/>
+    <hyperlink ref="G97" r:id="rId49"/>
+    <hyperlink ref="G99" r:id="rId50"/>
+    <hyperlink ref="F99" r:id="rId51"/>
+    <hyperlink ref="F101" r:id="rId52"/>
+    <hyperlink ref="F105" r:id="rId53"/>
+    <hyperlink ref="F107" r:id="rId54"/>
+    <hyperlink ref="F110" r:id="rId55"/>
+    <hyperlink ref="G110" r:id="rId56"/>
+    <hyperlink ref="F112" r:id="rId57"/>
+    <hyperlink ref="F8" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId58"/>
+  <pageSetup orientation="portrait" r:id="rId59"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA0E22C9-513F-4EC7-AEFF-575565EAE399}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="47.44140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="33.109375" customWidth="1"/>
-    <col min="6" max="6" width="30.21875" customWidth="1"/>
+    <col min="3" max="3" width="47.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="34.140625" customWidth="1"/>
+    <col min="5" max="5" width="33.140625" customWidth="1"/>
+    <col min="6" max="6" width="30.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17">
       <c r="A1" s="4" t="s">
         <v>141</v>
       </c>
@@ -3653,7 +3662,7 @@
       <c r="N1" s="4"/>
       <c r="Q1" s="4"/>
     </row>
-    <row r="2" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="30">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3664,7 +3673,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="30">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3675,7 +3684,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="30">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3686,7 +3695,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="30">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3697,7 +3706,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="30">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3708,7 +3717,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="30">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3725,17 +3734,17 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A00DF19-61A6-4AD7-9E72-F7B7A5E110F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.109375" customWidth="1"/>
-    <col min="2" max="2" width="41.109375" style="2" customWidth="1"/>
-    <col min="3" max="4" width="48.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="35.88671875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" customWidth="1"/>
+    <col min="2" max="2" width="41.140625" style="2" customWidth="1"/>
+    <col min="3" max="4" width="48.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="35.85546875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="3" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>141</v>
       </c>
@@ -3752,7 +3761,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="45">
       <c r="A2">
         <v>66</v>
       </c>
@@ -3766,7 +3775,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="45">
       <c r="A4">
         <v>67</v>
       </c>
@@ -3780,7 +3789,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="45">
       <c r="A5">
         <v>68</v>
       </c>
@@ -3794,7 +3803,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="45">
       <c r="A8">
         <v>69</v>
       </c>
@@ -3808,7 +3817,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="45">
       <c r="A10">
         <v>70</v>
       </c>
@@ -3819,7 +3828,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="45">
       <c r="A12">
         <v>71</v>
       </c>
@@ -3830,7 +3839,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="45">
       <c r="A14">
         <v>72</v>
       </c>
@@ -3841,7 +3850,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="45">
       <c r="A16">
         <v>73</v>
       </c>
@@ -3849,7 +3858,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="45">
       <c r="A18">
         <v>74</v>
       </c>
@@ -3857,7 +3866,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="45">
       <c r="A20">
         <v>75</v>
       </c>
@@ -3865,7 +3874,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="45">
       <c r="A22">
         <v>76</v>
       </c>
@@ -3873,7 +3882,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="45">
       <c r="A24">
         <v>77</v>
       </c>
@@ -3884,7 +3893,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="45">
       <c r="A26">
         <v>80</v>
       </c>
@@ -3895,7 +3904,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" ht="45">
       <c r="A33">
         <v>83</v>
       </c>
@@ -3905,14 +3914,35 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C16" r:id="rId1" xr:uid="{647997EC-A63E-42C8-8724-95F124BE8E7E}"/>
-    <hyperlink ref="C18" r:id="rId2" xr:uid="{DDADA295-28D7-48DB-B492-DC62029C4AFA}"/>
-    <hyperlink ref="C20" r:id="rId3" xr:uid="{498C3B35-9E6F-42A7-AC21-90C477670151}"/>
-    <hyperlink ref="C22" r:id="rId4" xr:uid="{271E3D14-8EB4-489F-A3DA-4D045292166C}"/>
-    <hyperlink ref="C12" r:id="rId5" xr:uid="{AFAD82DC-CCAE-49D0-8FAF-FD4D01BB3AFC}"/>
-    <hyperlink ref="C24" r:id="rId6" xr:uid="{28ADFEF8-90F5-4B44-951A-8D87E706AA2E}"/>
-    <hyperlink ref="B5" r:id="rId7" xr:uid="{4BE34D5B-11F0-4977-8ACC-B9C48CD9A853}"/>
+    <hyperlink ref="C16" r:id="rId1"/>
+    <hyperlink ref="C18" r:id="rId2"/>
+    <hyperlink ref="C20" r:id="rId3"/>
+    <hyperlink ref="C22" r:id="rId4"/>
+    <hyperlink ref="C12" r:id="rId5"/>
+    <hyperlink ref="C24" r:id="rId6"/>
+    <hyperlink ref="B5" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A2:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="27.75">
+      <c r="A3" s="15" t="s">
+        <v>363</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/curriculum_videos.xlsx
+++ b/curriculum_videos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="15600" windowHeight="11760" activeTab="6"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="15600" windowHeight="11760" firstSheet="5" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="CM" sheetId="1" r:id="rId1"/>
@@ -14,6 +14,8 @@
     <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
     <sheet name="APT HW" sheetId="4" r:id="rId6"/>
     <sheet name="APT_Notes" sheetId="7" r:id="rId7"/>
+    <sheet name="Simple LinearRegression" sheetId="8" r:id="rId8"/>
+    <sheet name="Multiple Linear Regression" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="429">
   <si>
     <t>CL72</t>
   </si>
@@ -1129,13 +1131,238 @@
   </si>
   <si>
     <t>Images location in colab try this if not displayed</t>
+  </si>
+  <si>
+    <t>Evaluation for linear regression model</t>
+  </si>
+  <si>
+    <t>R - squared: shud be closed to 1</t>
+  </si>
+  <si>
+    <t>it is 1- (SSE/SST)</t>
+  </si>
+  <si>
+    <t>Can also be computed by np.corrcoef()</t>
+  </si>
+  <si>
+    <t>∑(y-ypred)^2</t>
+  </si>
+  <si>
+    <t>SSE=</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SST = </t>
+  </si>
+  <si>
+    <t>∑(y-ymean)^2</t>
+  </si>
+  <si>
+    <t>MSE</t>
+  </si>
+  <si>
+    <t>Mean Squared errors</t>
+  </si>
+  <si>
+    <t>should be close to 0</t>
+  </si>
+  <si>
+    <t>MSE=</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1/n </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>∑ (yactual-ypredicted)^2</t>
+    </r>
+  </si>
+  <si>
+    <t>RMSE is root mean squared errors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RMSE = </t>
+  </si>
+  <si>
+    <t>√MSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAE </t>
+  </si>
+  <si>
+    <t>Mean absolute errors</t>
+  </si>
+  <si>
+    <t>MAE=</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1/n </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>∑| yactual-ypredicted |</t>
+    </r>
+  </si>
+  <si>
+    <t>y = mx+c</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">slope m =( </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>∑(xi-xmean) (yi-ymean)  )   /   ∑(xi-xmean)^2</t>
+    </r>
+  </si>
+  <si>
+    <t>intercept c=</t>
+  </si>
+  <si>
+    <t>ymean-m*xmean</t>
+  </si>
+  <si>
+    <t>USING MATHS</t>
+  </si>
+  <si>
+    <t>USING SKLEARN MODULE</t>
+  </si>
+  <si>
+    <t>steps</t>
+  </si>
+  <si>
+    <t>get the slope and  intercept</t>
+  </si>
+  <si>
+    <t>create an instance of the model   - LinearRegression()</t>
+  </si>
+  <si>
+    <t>fit training data to the model - .fit ()</t>
+  </si>
+  <si>
+    <t>slope = model.coef_</t>
+  </si>
+  <si>
+    <t>intercept = model.intercept_</t>
+  </si>
+  <si>
+    <t>predict using the model</t>
+  </si>
+  <si>
+    <t>predict y train or y test using above model</t>
+  </si>
+  <si>
+    <t>Evaluate calculating metrics R2, MSE, RMSE, MAE</t>
+  </si>
+  <si>
+    <t>Residual/Error analysis</t>
+  </si>
+  <si>
+    <t>For best fit line (i.ebest model/regression line)Mean of the random errors shud be zero</t>
+  </si>
+  <si>
+    <t>you can check with histogram</t>
+  </si>
+  <si>
+    <t>you cancheck by normal distribution curve using probablity density function  formula</t>
+  </si>
+  <si>
+    <t>standard function Is norm.pdf() from scipy.stats module</t>
+  </si>
+  <si>
+    <t> Homoscedasticity &amp; Heteroscedasticity</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> check for the trend in the scatter plot between the errors and the feature and target variables. There should not be a trend.</t>
+  </si>
+  <si>
+    <t>Homescedasticity</t>
+  </si>
+  <si>
+    <t>heteroscedasticity</t>
+  </si>
+  <si>
+    <t>no variance or error variance is constant. This is good</t>
+  </si>
+  <si>
+    <t>variation in error variance. This is not good</t>
+  </si>
+  <si>
+    <t>Simple Linear regression model (Class 58 to 61)</t>
+  </si>
+  <si>
+    <t>cl61</t>
+  </si>
+  <si>
+    <t>https://github.com/nalinis07/APT_Ref_Copy_Links/blob/MASTER/AT_Lesson_61_Reference.ipynb</t>
+  </si>
+  <si>
+    <t>cl62</t>
+  </si>
+  <si>
+    <t>cl58</t>
+  </si>
+  <si>
+    <t>cl59</t>
+  </si>
+  <si>
+    <t>can use sklearn module to build the model and get intercept and regression co-efficients</t>
+  </si>
+  <si>
+    <t>can also use statsmodel.api module for model and regression co-efficients</t>
+  </si>
+  <si>
+    <t>sm.add_constant</t>
+  </si>
+  <si>
+    <t>sm.OLS(y_train, X_train_sm).fit()</t>
+  </si>
+  <si>
+    <t>sm_lin_reg.params</t>
+  </si>
+  <si>
+    <t>model.summary - gives intercept , regression co-efficients, r2 score, adjusted r2, p-value etc, multicollinearity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for a feature to be statistically significant its p-value listed in summry() shud be less than 0.05. </t>
+  </si>
+  <si>
+    <t>else remove that feature</t>
+  </si>
+  <si>
+    <t>https://github.com/nalinis07/APT_Ref_Copy_Links/blob/MASTER/Nals_Lesson_62_Reference.ipynb</t>
+  </si>
+  <si>
+    <t>https://github.com/nalinis07/APT_Ref_Copy_Links/blob/MASTER/Nalini_Lesson_63_Reference.ipynb</t>
+  </si>
+  <si>
+    <t>cl63</t>
+  </si>
+  <si>
+    <t>Multiple linear regression )class 62)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1164,13 +1391,47 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="21"/>
       <color rgb="FF0000FF"/>
       <name val="Courier New"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1192,6 +1453,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1233,7 +1500,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1273,7 +1540,31 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1290,6 +1581,58 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2053" name="Picture 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="9525000"/>
+          <a:ext cx="2124075" cy="638175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="1">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1547,7 +1890,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1888,7 +2231,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P229"/>
+  <dimension ref="A1:P234"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="2"/>
@@ -1974,7 +2317,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:16" s="10" customFormat="1" ht="30.75" thickBot="1">
+    <row r="7" spans="1:16" s="10" customFormat="1" ht="30">
       <c r="A7" s="10" t="s">
         <v>81</v>
       </c>
@@ -1983,1045 +2326,1048 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:16" s="13" customFormat="1" ht="30.75" thickBot="1">
-      <c r="A8" s="12" t="s">
+    <row r="8" spans="1:16" s="10" customFormat="1">
+      <c r="B8" s="11"/>
+    </row>
+    <row r="9" spans="1:16" s="20" customFormat="1">
+      <c r="A9" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" s="21"/>
+    </row>
+    <row r="10" spans="1:16" s="20" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A10" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B10" s="21"/>
+    </row>
+    <row r="11" spans="1:16" s="24" customFormat="1" ht="30.75" thickBot="1">
+      <c r="A11" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B11" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F11" s="23" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15.75" thickBot="1">
-      <c r="B9" s="5"/>
-    </row>
-    <row r="10" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
-      <c r="A10" s="12" t="s">
+    <row r="12" spans="1:16" s="20" customFormat="1">
+      <c r="A12" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="B12" s="21"/>
+      <c r="F12" s="25" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="10" customFormat="1">
+      <c r="A13" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="F13" s="19" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="10" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A14" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="F14" s="19" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
+      <c r="A15" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="F10" s="13" t="s">
+      <c r="B15" s="14"/>
+      <c r="F15" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G15" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="O10" s="13" t="s">
+      <c r="O15" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="P10" s="13" t="s">
+      <c r="P15" s="13" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15.75" thickBot="1">
-      <c r="B11" s="5"/>
-    </row>
-    <row r="12" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
-      <c r="A12" s="12" t="s">
+    <row r="16" spans="1:16" ht="15.75" thickBot="1">
+      <c r="B16" s="5"/>
+    </row>
+    <row r="17" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
+      <c r="A17" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="F12" s="13" t="s">
+      <c r="B17" s="14"/>
+      <c r="F17" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G17" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="O12" s="13" t="s">
+      <c r="O17" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="P12" s="13" t="s">
+      <c r="P17" s="13" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15.75" thickBot="1">
-      <c r="B13" s="5"/>
-    </row>
-    <row r="14" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
-      <c r="A14" s="12" t="s">
+    <row r="18" spans="1:16" ht="15.75" thickBot="1">
+      <c r="B18" s="5"/>
+    </row>
+    <row r="19" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
+      <c r="A19" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="F14" s="14" t="s">
+      <c r="B19" s="14"/>
+      <c r="F19" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G19" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="O14" s="13" t="s">
+      <c r="O19" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="P14" s="13" t="s">
+      <c r="P19" s="13" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15.75" thickBot="1">
-      <c r="B15" s="5"/>
-    </row>
-    <row r="16" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
-      <c r="A16" s="12" t="s">
+    <row r="20" spans="1:16" ht="15.75" thickBot="1">
+      <c r="B20" s="5"/>
+    </row>
+    <row r="21" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
+      <c r="A21" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B21" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F21" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G21" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="O16" s="13" t="s">
+      <c r="O21" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="P16" s="13" t="s">
+      <c r="P21" s="13" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="30.75" thickBot="1">
-      <c r="F17" s="2" t="s">
+    <row r="22" spans="1:16" ht="30.75" thickBot="1">
+      <c r="F22" s="2" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="18" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
-      <c r="A18" s="12" t="s">
+    <row r="23" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
+      <c r="A23" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F23" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G23" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="O18" s="13" t="s">
+      <c r="O23" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="P18" s="13" t="s">
+      <c r="P23" s="13" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="15.75" thickBot="1"/>
-    <row r="20" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
-      <c r="A20" s="12" t="s">
+    <row r="24" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="25" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
+      <c r="A25" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F25" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G25" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="O20" s="13" t="s">
+      <c r="O25" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="P20" s="13" t="s">
+      <c r="P25" s="13" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="15.75" thickBot="1"/>
-    <row r="22" spans="1:16" s="13" customFormat="1" ht="30.75" thickBot="1">
-      <c r="A22" s="12" t="s">
+    <row r="26" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="27" spans="1:16" s="13" customFormat="1" ht="30.75" thickBot="1">
+      <c r="A27" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B27" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F27" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G27" s="14" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="15.75" thickBot="1"/>
-    <row r="24" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
-      <c r="A24" s="12" t="s">
+    <row r="28" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="29" spans="1:16" s="13" customFormat="1" ht="45.75" thickBot="1">
+      <c r="A29" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B29" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F29" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="G24" s="13" t="s">
+      <c r="G29" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="O24" s="13" t="s">
+      <c r="O29" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="P24" s="14" t="s">
+      <c r="P29" s="14" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="15.75" thickBot="1"/>
-    <row r="26" spans="1:16" s="13" customFormat="1" ht="30.75" thickBot="1">
-      <c r="A26" s="12" t="s">
+    <row r="30" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="31" spans="1:16" s="13" customFormat="1" ht="30.75" thickBot="1">
+      <c r="A31" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B31" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F31" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="G26" s="14" t="s">
+      <c r="G31" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="O26" s="13" t="s">
+      <c r="O31" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="P26" s="13" t="s">
+      <c r="P31" s="13" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="15.75" thickBot="1"/>
-    <row r="28" spans="1:16" s="13" customFormat="1" ht="27.6" customHeight="1" thickBot="1">
-      <c r="A28" s="12" t="s">
+    <row r="32" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="33" spans="1:16" s="13" customFormat="1" ht="27.6" customHeight="1" thickBot="1">
+      <c r="A33" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B33" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F33" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="G28" s="14" t="s">
+      <c r="G33" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="O28" s="13" t="s">
+      <c r="O33" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="P28" s="13" t="s">
+      <c r="P33" s="13" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="15.75" thickBot="1"/>
-    <row r="30" spans="1:16" s="13" customFormat="1" ht="30.75" thickBot="1">
-      <c r="A30" s="12" t="s">
+    <row r="34" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="35" spans="1:16" s="13" customFormat="1" ht="30.75" thickBot="1">
+      <c r="A35" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F35" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="G30" s="14" t="s">
+      <c r="G35" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="O30" s="13" t="s">
+      <c r="O35" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="P30" s="13" t="s">
+      <c r="P35" s="13" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="15.75" thickBot="1"/>
-    <row r="32" spans="1:16" s="13" customFormat="1" ht="30.75" thickBot="1">
-      <c r="A32" s="12" t="s">
+    <row r="36" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="37" spans="1:16" s="13" customFormat="1" ht="30.75" thickBot="1">
+      <c r="A37" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F37" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="G37" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="O32" s="13" t="s">
+      <c r="O37" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="P32" s="13" t="s">
+      <c r="P37" s="13" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="2" t="s">
+    <row r="39" spans="1:16">
+      <c r="A39" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B39" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="45">
-      <c r="B35" s="2" t="s">
+    <row r="40" spans="1:16" ht="45">
+      <c r="B40" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="2" t="s">
+    <row r="41" spans="1:16">
+      <c r="A41" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B41" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="2" t="s">
+    <row r="42" spans="1:16">
+      <c r="A42" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B42" s="5" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="2" t="s">
+    <row r="43" spans="1:16">
+      <c r="A43" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B43" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
-      <c r="B39" s="2" t="s">
+    <row r="44" spans="1:16">
+      <c r="B44" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="2" t="s">
+    <row r="45" spans="1:16">
+      <c r="A45" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B45" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
-      <c r="B41" s="5" t="s">
+    <row r="46" spans="1:16">
+      <c r="B46" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="2" t="s">
+    <row r="47" spans="1:16">
+      <c r="A47" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="2" t="s">
+    <row r="49" spans="1:5">
+      <c r="A49" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B49" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
-      <c r="B45" s="2" t="s">
+    <row r="50" spans="1:5">
+      <c r="B50" s="2" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="B48" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="B51" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="B53" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="B56" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
-      <c r="B53" s="5" t="s">
+    <row r="58" spans="1:5">
+      <c r="B58" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
-      <c r="B54" s="2" t="s">
+    <row r="59" spans="1:5">
+      <c r="B59" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="150">
-      <c r="A56" s="2">
+    <row r="61" spans="1:5" ht="150">
+      <c r="A61" s="2">
         <v>132</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B61" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E61" s="2" t="s">
         <v>120</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="180">
-      <c r="A58" s="2">
-        <v>133</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="90">
-      <c r="E59" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="180">
-      <c r="A60" s="2">
-        <v>134</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="90">
-      <c r="E61" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="180">
       <c r="A63" s="2">
-        <v>135</v>
+        <v>133</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="90">
+      <c r="E64" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:16" ht="180">
       <c r="A65" s="2">
+        <v>134</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" ht="90">
+      <c r="E66" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="180">
+      <c r="A68" s="2">
+        <v>135</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="180">
+      <c r="A70" s="2">
         <v>136</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="E70" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="180">
-      <c r="A67" s="2">
+    <row r="72" spans="1:16" ht="180">
+      <c r="A72" s="2">
         <v>137</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="E72" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="180">
-      <c r="A69" s="2">
+    <row r="74" spans="1:16" ht="180">
+      <c r="A74" s="2">
         <v>138</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="E74" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="O69" s="2" t="s">
+      <c r="O74" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="P69" s="6" t="s">
+      <c r="P74" s="6" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="70" spans="1:16" ht="165">
-      <c r="E70" s="2" t="s">
+    <row r="75" spans="1:16" ht="165">
+      <c r="E75" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="71" spans="1:16" ht="180">
-      <c r="A71" s="2">
+    <row r="76" spans="1:16" ht="180">
+      <c r="A76" s="2">
         <v>139</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="E76" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="O71" s="7" t="s">
+      <c r="O76" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="P71" s="2" t="s">
+      <c r="P76" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="73" spans="1:16" ht="180">
-      <c r="A73" s="2">
+    <row r="78" spans="1:16" ht="180">
+      <c r="A78" s="2">
         <v>140</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="E78" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="O73" s="7" t="s">
+      <c r="O78" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="P73" s="5" t="s">
+      <c r="P78" s="5" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="74" spans="1:16" ht="45">
-      <c r="O74" s="2" t="s">
+    <row r="79" spans="1:16" ht="45">
+      <c r="O79" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="P74" s="2" t="s">
+      <c r="P79" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="75" spans="1:16" ht="180">
-      <c r="A75" s="2">
+    <row r="80" spans="1:16" ht="180">
+      <c r="A80" s="2">
         <v>141</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="E80" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="P75" s="2" t="s">
+      <c r="P80" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="77" spans="1:16" ht="180">
-      <c r="A77" s="2">
+    <row r="82" spans="1:16" ht="180">
+      <c r="A82" s="2">
         <v>142</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="E82" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="P77" s="2" t="s">
+      <c r="P82" s="2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="79" spans="1:16" ht="180">
-      <c r="A79" s="2">
+    <row r="84" spans="1:16" ht="180">
+      <c r="A84" s="2">
         <v>143</v>
       </c>
-      <c r="E79" s="2" t="s">
+      <c r="E84" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="P79" s="5" t="s">
+      <c r="P84" s="5" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="80" spans="1:16">
-      <c r="P80" s="2" t="s">
+    <row r="85" spans="1:16">
+      <c r="P85" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="81" spans="1:16" ht="90">
-      <c r="P81" s="8" t="s">
+    <row r="86" spans="1:16" ht="90">
+      <c r="P86" s="8" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="82" spans="1:16" ht="195">
-      <c r="A82" s="2">
+    <row r="87" spans="1:16" ht="195">
+      <c r="A87" s="2">
         <v>144</v>
       </c>
-      <c r="E82" s="2" t="s">
+      <c r="E87" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="P82" s="6" t="s">
+      <c r="P87" s="6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="83" spans="1:16" ht="30">
-      <c r="P83" s="6" t="s">
+    <row r="88" spans="1:16" ht="30">
+      <c r="P88" s="6" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="30">
-      <c r="A88" s="2">
+    <row r="93" spans="1:16" ht="30">
+      <c r="A93" s="2">
         <v>78</v>
       </c>
-      <c r="F88" s="2" t="s">
+      <c r="F93" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="G88" s="5" t="s">
+      <c r="G93" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="O88" s="2" t="s">
+      <c r="O93" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="89" spans="1:16" ht="30">
-      <c r="G89" s="5" t="s">
+    <row r="94" spans="1:16" ht="30">
+      <c r="G94" s="5" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="90" spans="1:16" ht="15.75" thickBot="1"/>
-    <row r="91" spans="1:16" ht="45.75" thickBot="1">
-      <c r="A91" s="2">
+    <row r="95" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="96" spans="1:16" ht="45.75" thickBot="1">
+      <c r="A96" s="2">
         <v>79</v>
       </c>
-      <c r="F91" s="5" t="s">
+      <c r="F96" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="G91" s="2" t="s">
+      <c r="G96" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="O91" s="13" t="s">
+      <c r="O96" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="P91" s="14" t="s">
+      <c r="P96" s="14" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="93" spans="1:16" ht="45">
-      <c r="A93" s="2">
+    <row r="98" spans="1:16" ht="45">
+      <c r="A98" s="2">
         <v>80</v>
       </c>
-      <c r="F93" s="5" t="s">
+      <c r="F98" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="G93" s="5" t="s">
+      <c r="G98" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="O93" s="2" t="s">
+      <c r="O98" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="P93" s="2" t="s">
+      <c r="P98" s="2" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="95" spans="1:16" ht="45">
-      <c r="A95" s="2">
+    <row r="100" spans="1:16" ht="45">
+      <c r="A100" s="2">
         <v>81</v>
       </c>
-      <c r="F95" s="5" t="s">
+      <c r="F100" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="G95" s="2" t="s">
+      <c r="G100" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="O95" s="2" t="s">
+      <c r="O100" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="P95" s="2" t="s">
+      <c r="P100" s="2" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="97" spans="1:16" ht="45">
-      <c r="A97" s="2">
+    <row r="102" spans="1:16" ht="45">
+      <c r="A102" s="2">
         <v>82</v>
       </c>
-      <c r="F97" s="5" t="s">
+      <c r="F102" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="G97" s="5" t="s">
+      <c r="G102" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="O97" s="2" t="s">
+      <c r="O102" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="P97" s="2" t="s">
+      <c r="P102" s="2" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="99" spans="1:16" ht="45">
-      <c r="A99" s="2">
+    <row r="104" spans="1:16" ht="45">
+      <c r="A104" s="2">
         <v>83</v>
       </c>
-      <c r="F99" s="5" t="s">
+      <c r="F104" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G99" s="5" t="s">
+      <c r="G104" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="O99" s="2" t="s">
+      <c r="O104" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="P99" s="2" t="s">
+      <c r="P104" s="2" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="101" spans="1:16" ht="45">
-      <c r="A101" s="2">
+    <row r="106" spans="1:16" ht="45">
+      <c r="A106" s="2">
         <v>84</v>
       </c>
-      <c r="F101" s="5" t="s">
+      <c r="F106" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="G101" s="5" t="s">
+      <c r="G106" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="O101" s="2" t="s">
+      <c r="O106" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="P101" s="2" t="s">
+      <c r="P106" s="2" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="45">
-      <c r="A103" s="2">
+    <row r="108" spans="1:16" ht="45">
+      <c r="A108" s="2">
         <v>85</v>
       </c>
-      <c r="F103" s="2" t="s">
+      <c r="F108" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G103" s="5" t="s">
+      <c r="G108" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="O103" s="2" t="s">
+      <c r="O108" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="P103" s="2" t="s">
+      <c r="P108" s="2" t="s">
         <v>220</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" ht="45">
-      <c r="A105" s="2">
-        <v>86</v>
-      </c>
-      <c r="F105" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="G105" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="O105" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="P105" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" ht="36" customHeight="1">
-      <c r="O106" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="P106" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" ht="45">
-      <c r="A107" s="2">
-        <v>87</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="G107" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="O107" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="P107" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" ht="45">
-      <c r="O108" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="P108" s="2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="110" spans="1:16" ht="45">
       <c r="A110" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>362</v>
+        <v>234</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="P110" s="2" t="s">
-        <v>246</v>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" ht="36" customHeight="1">
+      <c r="O111" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="P111" s="2" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="112" spans="1:16" ht="45">
       <c r="A112" s="2">
+        <v>87</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="O112" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="P112" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="45">
+      <c r="O113" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="P113" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="45">
+      <c r="A115" s="2">
+        <v>88</v>
+      </c>
+      <c r="F115" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="O115" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="P115" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" ht="45">
+      <c r="A117" s="2">
         <v>89</v>
       </c>
-      <c r="F112" s="5" t="s">
+      <c r="F117" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="O112" s="2" t="s">
+      <c r="O117" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="P112" s="2" t="s">
+      <c r="P117" s="2" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="114" spans="1:16" ht="45">
-      <c r="A114" s="2">
+    <row r="119" spans="1:16" ht="45">
+      <c r="A119" s="2">
         <v>90</v>
       </c>
-      <c r="F114" s="2" t="s">
+      <c r="F119" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="O114" s="2" t="s">
+      <c r="O119" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="P114" s="2" t="s">
+      <c r="P119" s="2" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="116" spans="1:16" ht="30">
-      <c r="A116" s="2">
+    <row r="121" spans="1:16" ht="30">
+      <c r="A121" s="2">
         <v>91</v>
       </c>
-      <c r="F116" s="5" t="s">
+      <c r="F121" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="O116" s="2" t="s">
+      <c r="O121" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="118" spans="1:16" ht="45">
-      <c r="A118" s="2">
+    <row r="123" spans="1:16" ht="45">
+      <c r="A123" s="2">
         <v>92</v>
       </c>
-      <c r="F118" s="5" t="s">
+      <c r="F123" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="O118" s="2" t="s">
+      <c r="O123" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="P118" s="2" t="s">
+      <c r="P123" s="2" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="120" spans="1:16" ht="45">
-      <c r="A120" s="2">
+    <row r="125" spans="1:16" ht="45">
+      <c r="A125" s="2">
         <v>93</v>
       </c>
-      <c r="F120" s="2" t="s">
+      <c r="F125" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="O120" s="2" t="s">
+      <c r="O125" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="P120" s="2" t="s">
+      <c r="P125" s="2" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="122" spans="1:16" ht="45">
-      <c r="A122" s="2">
+    <row r="127" spans="1:16" ht="45">
+      <c r="A127" s="2">
         <v>94</v>
       </c>
-      <c r="F122" s="5" t="s">
+      <c r="F127" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="O122" s="2" t="s">
+      <c r="O127" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="P122" s="2" t="s">
+      <c r="P127" s="2" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="124" spans="1:16" ht="45">
-      <c r="A124" s="2">
+    <row r="129" spans="1:16" ht="45">
+      <c r="A129" s="2">
         <v>95</v>
       </c>
-      <c r="F124" s="2" t="s">
+      <c r="F129" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="O124" s="2" t="s">
+      <c r="O129" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="P124" s="2" t="s">
+      <c r="P129" s="2" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="126" spans="1:16" ht="45">
-      <c r="A126" s="2">
+    <row r="131" spans="1:16" ht="45">
+      <c r="A131" s="2">
         <v>96</v>
       </c>
-      <c r="F126" s="2" t="s">
+      <c r="F131" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="O126" s="2" t="s">
+      <c r="O131" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="P126" s="2" t="s">
+      <c r="P131" s="2" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="127" spans="1:16" ht="15.75" thickBot="1"/>
-    <row r="128" spans="1:16" ht="45.75" thickBot="1">
-      <c r="A128" s="2">
+    <row r="132" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="133" spans="1:16" ht="45.75" thickBot="1">
+      <c r="A133" s="2">
         <v>97</v>
       </c>
-      <c r="F128" s="2" t="s">
+      <c r="F133" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="O128" s="13" t="s">
+      <c r="O133" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="P128" s="13" t="s">
+      <c r="P133" s="13" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="130" spans="1:16" ht="25.15" customHeight="1">
-      <c r="A130" s="2">
+    <row r="135" spans="1:16" ht="25.15" customHeight="1">
+      <c r="A135" s="2">
         <v>98</v>
       </c>
-      <c r="F130" s="2" t="s">
+      <c r="F135" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="O130" s="2" t="s">
+      <c r="O135" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="P130" s="2" t="s">
+      <c r="P135" s="2" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="132" spans="1:16" ht="29.45" customHeight="1">
-      <c r="A132" s="2">
+    <row r="137" spans="1:16" ht="29.45" customHeight="1">
+      <c r="A137" s="2">
         <v>99</v>
       </c>
-      <c r="F132" s="2" t="s">
+      <c r="F137" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="O132" s="2" t="s">
+      <c r="O137" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="P132" s="2" t="s">
+      <c r="P137" s="2" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="134" spans="1:16" ht="33.6" customHeight="1">
-      <c r="A134" s="2">
+    <row r="139" spans="1:16" ht="33.6" customHeight="1">
+      <c r="A139" s="2">
         <v>100</v>
       </c>
-      <c r="F134" s="5" t="s">
+      <c r="F139" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="O134" s="2" t="s">
+      <c r="O139" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="P134" s="2" t="s">
+      <c r="P139" s="2" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="136" spans="1:16" ht="45">
-      <c r="A136" s="2">
+    <row r="141" spans="1:16" ht="45">
+      <c r="A141" s="2">
         <v>101</v>
       </c>
-      <c r="F136" s="2" t="s">
+      <c r="F141" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="O136" s="2" t="s">
+      <c r="O141" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="P136" s="2" t="s">
+      <c r="P141" s="2" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="138" spans="1:16" ht="27" customHeight="1">
-      <c r="A138" s="2">
+    <row r="143" spans="1:16" ht="27" customHeight="1">
+      <c r="A143" s="2">
         <v>102</v>
       </c>
-      <c r="F138" s="2" t="s">
+      <c r="F143" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="O138" s="2" t="s">
+      <c r="O143" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="P138" s="2" t="s">
+      <c r="P143" s="2" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="140" spans="1:16" ht="32.450000000000003" customHeight="1">
-      <c r="A140" s="2">
+    <row r="145" spans="1:16" ht="32.450000000000003" customHeight="1">
+      <c r="A145" s="2">
         <v>103</v>
       </c>
-      <c r="F140" s="2" t="s">
+      <c r="F145" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="O140" s="2" t="s">
+      <c r="O145" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="142" spans="1:16" ht="27" customHeight="1">
-      <c r="A142" s="2">
+    <row r="147" spans="1:16" ht="27" customHeight="1">
+      <c r="A147" s="2">
         <v>104</v>
       </c>
-      <c r="F142" s="2" t="s">
+      <c r="F147" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="O142" s="2" t="s">
+      <c r="O147" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="144" spans="1:16" ht="27.6" customHeight="1">
-      <c r="A144" s="2">
+    <row r="149" spans="1:16" ht="27.6" customHeight="1">
+      <c r="A149" s="2">
         <v>105</v>
       </c>
-      <c r="F144" s="2" t="s">
+      <c r="F149" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="O144" s="2" t="s">
+      <c r="O149" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="P144" s="2" t="s">
+      <c r="P149" s="2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="146" spans="1:16" ht="27.6" customHeight="1">
-      <c r="A146" s="2">
+    <row r="151" spans="1:16" ht="27.6" customHeight="1">
+      <c r="A151" s="2">
         <v>106</v>
       </c>
-      <c r="F146" s="2" t="s">
+      <c r="F151" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="O146" s="2" t="s">
+      <c r="O151" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="P146" s="2" t="s">
+      <c r="P151" s="2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="148" spans="1:16" ht="34.15" customHeight="1">
-      <c r="A148" s="2">
+    <row r="153" spans="1:16" ht="34.15" customHeight="1">
+      <c r="A153" s="2">
         <v>107</v>
       </c>
-      <c r="F148" s="2" t="s">
+      <c r="F153" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="O148" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="P148" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="150" spans="1:16" ht="35.450000000000003" customHeight="1">
-      <c r="A150" s="2">
-        <v>108</v>
-      </c>
-      <c r="F150" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="O150" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="P150" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="152" spans="1:16" ht="30.6" customHeight="1">
-      <c r="A152" s="2">
-        <v>109</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="O152" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="P152" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="153" spans="1:16" ht="45">
       <c r="O153" s="2" t="s">
         <v>263</v>
       </c>
@@ -3029,597 +3375,634 @@
         <v>262</v>
       </c>
     </row>
-    <row r="155" spans="1:16" ht="36" customHeight="1">
+    <row r="155" spans="1:16" ht="35.450000000000003" customHeight="1">
       <c r="A155" s="2">
+        <v>108</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="O155" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P155" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" ht="30.6" customHeight="1">
+      <c r="A157" s="2">
+        <v>109</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="O157" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P157" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" ht="45">
+      <c r="O158" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="P158" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" ht="36" customHeight="1">
+      <c r="A160" s="2">
         <v>110</v>
       </c>
-      <c r="F155" s="2" t="s">
+      <c r="F160" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="O155" s="2" t="s">
+      <c r="O160" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="P155" s="2" t="s">
+      <c r="P160" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="157" spans="1:16" ht="25.15" customHeight="1">
-      <c r="A157" s="2">
+    <row r="162" spans="1:16" ht="25.15" customHeight="1">
+      <c r="A162" s="2">
         <v>111</v>
       </c>
-      <c r="F157" s="2" t="s">
+      <c r="F162" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="O157" s="2" t="s">
+      <c r="O162" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="P157" s="2" t="s">
+      <c r="P162" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="159" spans="1:16" ht="30" customHeight="1">
-      <c r="A159" s="2">
+    <row r="164" spans="1:16" ht="30" customHeight="1">
+      <c r="A164" s="2">
         <v>112</v>
       </c>
-      <c r="F159" s="2" t="s">
+      <c r="F164" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="O159" s="2" t="s">
+      <c r="O164" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="P159" s="2" t="s">
+      <c r="P164" s="2" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="161" spans="1:16" ht="24" customHeight="1">
-      <c r="A161" s="2">
+    <row r="166" spans="1:16" ht="24" customHeight="1">
+      <c r="A166" s="2">
         <v>113</v>
       </c>
-      <c r="F161" s="2" t="s">
+      <c r="F166" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="O161" s="2" t="s">
+      <c r="O166" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="P161" s="2" t="s">
+      <c r="P166" s="2" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="163" spans="1:16" ht="45">
-      <c r="A163" s="2">
+    <row r="168" spans="1:16" ht="45">
+      <c r="A168" s="2">
         <v>114</v>
       </c>
-      <c r="F163" s="5" t="s">
+      <c r="F168" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="O163" s="2" t="s">
+      <c r="O168" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="P163" s="2" t="s">
+      <c r="P168" s="2" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="165" spans="1:16" ht="34.15" customHeight="1">
-      <c r="A165" s="2">
+    <row r="170" spans="1:16" ht="34.15" customHeight="1">
+      <c r="A170" s="2">
         <v>115</v>
       </c>
-      <c r="F165" s="2" t="s">
+      <c r="F170" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="O165" s="2" t="s">
+      <c r="O170" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="P165" s="2" t="s">
+      <c r="P170" s="2" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="167" spans="1:16" ht="25.9" customHeight="1">
-      <c r="A167" s="2">
+    <row r="172" spans="1:16" ht="25.9" customHeight="1">
+      <c r="A172" s="2">
         <v>116</v>
       </c>
-      <c r="F167" s="2" t="s">
+      <c r="F172" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="O167" s="2" t="s">
+      <c r="O172" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="P167" s="2" t="s">
+      <c r="P172" s="2" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="169" spans="1:16" ht="37.9" customHeight="1">
-      <c r="A169" s="2">
+    <row r="174" spans="1:16" ht="37.9" customHeight="1">
+      <c r="A174" s="2">
         <v>117</v>
       </c>
-      <c r="F169" s="2" t="s">
+      <c r="F174" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="O169" s="2" t="s">
+      <c r="O174" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="P169" s="2" t="s">
+      <c r="P174" s="2" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="171" spans="1:16" ht="37.15" customHeight="1">
-      <c r="A171" s="2">
+    <row r="176" spans="1:16" ht="37.15" customHeight="1">
+      <c r="A176" s="2">
         <v>118</v>
       </c>
-      <c r="F171" s="2" t="s">
+      <c r="F176" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="O171" s="2" t="s">
+      <c r="O176" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="P171" s="2" t="s">
+      <c r="P176" s="2" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="173" spans="1:16" ht="28.15" customHeight="1">
-      <c r="A173" s="2">
+    <row r="178" spans="1:16" ht="28.15" customHeight="1">
+      <c r="A178" s="2">
         <v>119</v>
       </c>
-      <c r="F173" s="2" t="s">
+      <c r="F178" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="O173" s="2" t="s">
+      <c r="O178" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="P173" s="2" t="s">
+      <c r="P178" s="2" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="175" spans="1:16" ht="39" customHeight="1">
-      <c r="A175" s="2">
+    <row r="180" spans="1:16" ht="39" customHeight="1">
+      <c r="A180" s="2">
         <v>120</v>
       </c>
-      <c r="F175" s="2" t="s">
+      <c r="F180" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="O175" s="2" t="s">
+      <c r="O180" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="P175" s="2" t="s">
+      <c r="P180" s="2" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="177" spans="1:16" ht="31.15" customHeight="1">
-      <c r="A177" s="2">
+    <row r="182" spans="1:16" ht="31.15" customHeight="1">
+      <c r="A182" s="2">
         <v>121</v>
       </c>
-      <c r="F177" s="2" t="s">
+      <c r="F182" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="O177" s="2" t="s">
+      <c r="O182" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="P177" s="2" t="s">
+      <c r="P182" s="2" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="179" spans="1:16" ht="34.9" customHeight="1">
-      <c r="A179" s="2">
+    <row r="184" spans="1:16" ht="34.9" customHeight="1">
+      <c r="A184" s="2">
         <v>122</v>
       </c>
-      <c r="F179" s="2" t="s">
+      <c r="F184" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="O179" s="2" t="s">
+      <c r="O184" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="P179" s="2" t="s">
+      <c r="P184" s="2" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="181" spans="1:16" ht="25.15" customHeight="1">
-      <c r="A181" s="2">
+    <row r="186" spans="1:16" ht="25.15" customHeight="1">
+      <c r="A186" s="2">
         <v>123</v>
       </c>
-      <c r="F181" s="2" t="s">
+      <c r="F186" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="O181" s="2" t="s">
+      <c r="O186" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="P181" s="2" t="s">
+      <c r="P186" s="2" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="183" spans="1:16" ht="50.45" customHeight="1">
-      <c r="A183" s="2">
+    <row r="188" spans="1:16" ht="50.45" customHeight="1">
+      <c r="A188" s="2">
         <v>124</v>
       </c>
-      <c r="F183" s="2" t="s">
+      <c r="F188" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="O183" s="2" t="s">
+      <c r="O188" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="P183" s="2" t="s">
+      <c r="P188" s="2" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="184" spans="1:16" ht="15.75" thickBot="1"/>
-    <row r="185" spans="1:16" ht="46.9" customHeight="1" thickBot="1">
-      <c r="A185" s="2">
+    <row r="189" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="190" spans="1:16" ht="46.9" customHeight="1" thickBot="1">
+      <c r="A190" s="2">
         <v>125</v>
       </c>
-      <c r="F185" s="2" t="s">
+      <c r="F190" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="O185" s="13" t="s">
+      <c r="O190" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="P185" s="14" t="s">
+      <c r="P190" s="14" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="186" spans="1:16" ht="15.75" thickBot="1"/>
-    <row r="187" spans="1:16" ht="58.15" customHeight="1" thickBot="1">
-      <c r="A187" s="2">
+    <row r="191" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="192" spans="1:16" ht="58.15" customHeight="1" thickBot="1">
+      <c r="A192" s="2">
         <v>126</v>
       </c>
-      <c r="F187" s="2" t="s">
+      <c r="F192" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="O187" s="13" t="s">
+      <c r="O192" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="P187" s="14" t="s">
+      <c r="P192" s="14" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="188" spans="1:16" ht="45">
-      <c r="O188" s="2" t="s">
+    <row r="193" spans="1:16" ht="45">
+      <c r="O193" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="P188" s="2" t="s">
+      <c r="P193" s="2" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="190" spans="1:16" ht="33" customHeight="1">
-      <c r="A190" s="2">
+    <row r="195" spans="1:16" ht="33" customHeight="1">
+      <c r="A195" s="2">
         <v>127</v>
       </c>
-      <c r="F190" s="2" t="s">
+      <c r="F195" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="O190" s="2" t="s">
+      <c r="O195" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="P190" s="2" t="s">
+      <c r="P195" s="2" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="193" spans="1:16" ht="33" customHeight="1">
-      <c r="A193" s="2">
+    <row r="198" spans="1:16" ht="33" customHeight="1">
+      <c r="A198" s="2">
         <v>128</v>
       </c>
-      <c r="F193" s="2" t="s">
+      <c r="F198" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="O193" s="2" t="s">
+      <c r="O198" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="195" spans="1:16" ht="46.15" customHeight="1">
-      <c r="A195" s="2">
+    <row r="200" spans="1:16" ht="46.15" customHeight="1">
+      <c r="A200" s="2">
         <v>129</v>
       </c>
-      <c r="F195" s="2" t="s">
+      <c r="F200" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="O195" s="2" t="s">
+      <c r="O200" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="197" spans="1:16" ht="31.15" customHeight="1">
-      <c r="A197" s="2">
+    <row r="202" spans="1:16" ht="31.15" customHeight="1">
+      <c r="A202" s="2">
         <v>130</v>
       </c>
-      <c r="F197" s="2" t="s">
+      <c r="F202" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="O197" s="2" t="s">
+      <c r="O202" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="P197" s="2" t="s">
+      <c r="P202" s="2" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="199" spans="1:16" ht="37.9" customHeight="1">
-      <c r="A199" s="2">
+    <row r="204" spans="1:16" ht="37.9" customHeight="1">
+      <c r="A204" s="2">
         <v>131</v>
       </c>
-      <c r="F199" s="2" t="s">
+      <c r="F204" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="O199" s="2" t="s">
+      <c r="O204" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="P199" s="2" t="s">
+      <c r="P204" s="2" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="201" spans="1:16" ht="28.15" customHeight="1">
-      <c r="A201" s="2">
+    <row r="206" spans="1:16" ht="28.15" customHeight="1">
+      <c r="A206" s="2">
         <v>132</v>
       </c>
-      <c r="F201" s="2" t="s">
+      <c r="F206" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="O201" s="2" t="s">
+      <c r="O206" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="P201" s="2" t="s">
+      <c r="P206" s="2" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="203" spans="1:16" ht="24" customHeight="1">
-      <c r="A203" s="2">
+    <row r="208" spans="1:16" ht="24" customHeight="1">
+      <c r="A208" s="2">
         <v>133</v>
       </c>
-      <c r="F203" s="2" t="s">
+      <c r="F208" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="O203" s="2" t="s">
+      <c r="O208" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="P203" s="2" t="s">
+      <c r="P208" s="2" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="204" spans="1:16" ht="23.45" customHeight="1"/>
-    <row r="205" spans="1:16" ht="42" customHeight="1">
-      <c r="A205" s="2">
+    <row r="209" spans="1:16" ht="23.45" customHeight="1"/>
+    <row r="210" spans="1:16" ht="42" customHeight="1">
+      <c r="A210" s="2">
         <v>134</v>
       </c>
-      <c r="F205" s="5" t="s">
+      <c r="F210" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="O205" s="2" t="s">
+      <c r="O210" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="P205" s="2" t="s">
+      <c r="P210" s="2" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="207" spans="1:16" ht="65.45" customHeight="1">
-      <c r="A207" s="2">
+    <row r="212" spans="1:16" ht="65.45" customHeight="1">
+      <c r="A212" s="2">
         <v>135</v>
       </c>
-      <c r="F207" s="2" t="s">
+      <c r="F212" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="O207" s="2" t="s">
+      <c r="O212" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="P207" s="2" t="s">
+      <c r="P212" s="2" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="208" spans="1:16" ht="45">
-      <c r="O208" s="2" t="s">
+    <row r="213" spans="1:16" ht="45">
+      <c r="O213" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="P208" s="2" t="s">
+      <c r="P213" s="2" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="210" spans="1:16" ht="40.15" customHeight="1">
-      <c r="O210" s="2" t="s">
+    <row r="215" spans="1:16" ht="40.15" customHeight="1">
+      <c r="O215" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="P210" s="2" t="s">
+      <c r="P215" s="2" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="211" spans="1:16" ht="28.15" customHeight="1">
-      <c r="A211" s="2">
+    <row r="216" spans="1:16" ht="28.15" customHeight="1">
+      <c r="A216" s="2">
         <v>136</v>
       </c>
-      <c r="F211" s="2" t="s">
+      <c r="F216" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="O211" s="2" t="s">
+      <c r="O216" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="P211" s="2" t="s">
+      <c r="P216" s="2" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="213" spans="1:16" ht="46.9" customHeight="1">
-      <c r="A213" s="2">
+    <row r="218" spans="1:16" ht="46.9" customHeight="1">
+      <c r="A218" s="2">
         <v>137</v>
       </c>
-      <c r="F213" s="2" t="s">
+      <c r="F218" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="O213" s="2" t="s">
+      <c r="O218" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="P213" s="2" t="s">
+      <c r="P218" s="2" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="215" spans="1:16" ht="46.9" customHeight="1">
-      <c r="A215" s="2">
+    <row r="220" spans="1:16" ht="46.9" customHeight="1">
+      <c r="A220" s="2">
         <v>138</v>
       </c>
-      <c r="F215" s="5" t="s">
+      <c r="F220" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="O215" s="2" t="s">
+      <c r="O220" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="P215" s="2" t="s">
+      <c r="P220" s="2" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="217" spans="1:16" ht="33" customHeight="1">
-      <c r="A217" s="2">
+    <row r="222" spans="1:16" ht="33" customHeight="1">
+      <c r="A222" s="2">
         <v>139</v>
       </c>
-      <c r="F217" s="2" t="s">
+      <c r="F222" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="O217" s="2" t="s">
+      <c r="O222" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="P217" s="2" t="s">
+      <c r="P222" s="2" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="219" spans="1:16" ht="63.6" customHeight="1">
-      <c r="A219" s="2">
+    <row r="224" spans="1:16" ht="63.6" customHeight="1">
+      <c r="A224" s="2">
         <v>140</v>
       </c>
-      <c r="F219" s="2" t="s">
+      <c r="F224" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="O219" s="2" t="s">
+      <c r="O224" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="P219" s="2" t="s">
+      <c r="P224" s="2" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="220" spans="1:16" ht="45">
-      <c r="O220" s="2" t="s">
+    <row r="225" spans="1:16" ht="45">
+      <c r="O225" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="P220" s="2" t="s">
+      <c r="P225" s="2" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="222" spans="1:16" ht="48.6" customHeight="1">
-      <c r="A222" s="2">
+    <row r="227" spans="1:16" ht="48.6" customHeight="1">
+      <c r="A227" s="2">
         <v>141</v>
       </c>
-      <c r="F222" s="2" t="s">
+      <c r="F227" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="P222" s="2" t="s">
+      <c r="P227" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="224" spans="1:16" ht="45" customHeight="1">
-      <c r="A224" s="2">
+    <row r="229" spans="1:16" ht="45" customHeight="1">
+      <c r="A229" s="2">
         <v>142</v>
       </c>
-      <c r="F224" s="2" t="s">
+      <c r="F229" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="O224" s="2" t="s">
+      <c r="O229" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="P224" s="2" t="s">
+      <c r="P229" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="225" spans="1:16" ht="30">
-      <c r="P225" s="2" t="s">
+    <row r="230" spans="1:16" ht="30">
+      <c r="P230" s="2" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="226" spans="1:16" ht="39.6" customHeight="1">
-      <c r="A226" s="2">
+    <row r="231" spans="1:16" ht="39.6" customHeight="1">
+      <c r="A231" s="2">
         <v>143</v>
       </c>
-      <c r="F226" s="2" t="s">
+      <c r="F231" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="O226" s="2" t="s">
+      <c r="O231" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="P226" s="2" t="s">
+      <c r="P231" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="227" spans="1:16" ht="30">
-      <c r="P227" s="2" t="s">
+    <row r="232" spans="1:16" ht="30">
+      <c r="P232" s="2" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="228" spans="1:16" ht="52.9" customHeight="1">
-      <c r="A228" s="2">
+    <row r="233" spans="1:16" ht="52.9" customHeight="1">
+      <c r="A233" s="2">
         <v>144</v>
       </c>
-      <c r="F228" s="2" t="s">
+      <c r="F233" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="P228" s="6" t="s">
+      <c r="P233" s="6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="229" spans="1:16" ht="30">
-      <c r="P229" s="6" t="s">
+    <row r="234" spans="1:16" ht="30">
+      <c r="P234" s="6" t="s">
         <v>122</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B41" r:id="rId1"/>
-    <hyperlink ref="B50" r:id="rId2"/>
-    <hyperlink ref="B53" r:id="rId3"/>
-    <hyperlink ref="B56" r:id="rId4"/>
+    <hyperlink ref="B46" r:id="rId1"/>
+    <hyperlink ref="B55" r:id="rId2"/>
+    <hyperlink ref="B58" r:id="rId3"/>
+    <hyperlink ref="B61" r:id="rId4"/>
     <hyperlink ref="B6" r:id="rId5"/>
-    <hyperlink ref="E71" r:id="rId6"/>
-    <hyperlink ref="B36" r:id="rId7"/>
-    <hyperlink ref="E69" r:id="rId8"/>
-    <hyperlink ref="P83" r:id="rId9"/>
-    <hyperlink ref="P82" r:id="rId10"/>
-    <hyperlink ref="P73" r:id="rId11"/>
-    <hyperlink ref="P69" r:id="rId12"/>
-    <hyperlink ref="G26" r:id="rId13"/>
-    <hyperlink ref="G10" r:id="rId14"/>
-    <hyperlink ref="F18" r:id="rId15"/>
-    <hyperlink ref="F20" r:id="rId16"/>
-    <hyperlink ref="F24" r:id="rId17"/>
-    <hyperlink ref="F26" r:id="rId18"/>
-    <hyperlink ref="F28" r:id="rId19"/>
-    <hyperlink ref="F30" r:id="rId20"/>
-    <hyperlink ref="F32" r:id="rId21"/>
-    <hyperlink ref="P24" r:id="rId22"/>
-    <hyperlink ref="G22" r:id="rId23"/>
-    <hyperlink ref="G12" r:id="rId24"/>
-    <hyperlink ref="G28" r:id="rId25"/>
-    <hyperlink ref="G30" r:id="rId26"/>
-    <hyperlink ref="F91" r:id="rId27"/>
-    <hyperlink ref="P91" r:id="rId28"/>
-    <hyperlink ref="G88" r:id="rId29"/>
-    <hyperlink ref="G101" r:id="rId30"/>
-    <hyperlink ref="G103" r:id="rId31"/>
-    <hyperlink ref="G105" r:id="rId32"/>
-    <hyperlink ref="F163" r:id="rId33"/>
-    <hyperlink ref="P185" r:id="rId34"/>
-    <hyperlink ref="P187" r:id="rId35"/>
-    <hyperlink ref="F205" r:id="rId36"/>
-    <hyperlink ref="F14" r:id="rId37" location="scrollTo=5f2emlnJM56A"/>
-    <hyperlink ref="F215" r:id="rId38"/>
-    <hyperlink ref="P79" r:id="rId39"/>
-    <hyperlink ref="P228" r:id="rId40"/>
-    <hyperlink ref="P229" r:id="rId41"/>
-    <hyperlink ref="B28" r:id="rId42"/>
-    <hyperlink ref="F93" r:id="rId43"/>
-    <hyperlink ref="G93" r:id="rId44"/>
-    <hyperlink ref="F95" r:id="rId45"/>
-    <hyperlink ref="F118" r:id="rId46"/>
-    <hyperlink ref="F134" r:id="rId47"/>
-    <hyperlink ref="F97" r:id="rId48"/>
-    <hyperlink ref="G97" r:id="rId49"/>
-    <hyperlink ref="G99" r:id="rId50"/>
-    <hyperlink ref="F99" r:id="rId51"/>
-    <hyperlink ref="F101" r:id="rId52"/>
-    <hyperlink ref="F105" r:id="rId53"/>
-    <hyperlink ref="F107" r:id="rId54"/>
-    <hyperlink ref="F110" r:id="rId55"/>
-    <hyperlink ref="G110" r:id="rId56"/>
-    <hyperlink ref="F112" r:id="rId57"/>
-    <hyperlink ref="F8" r:id="rId58"/>
+    <hyperlink ref="E76" r:id="rId6"/>
+    <hyperlink ref="B41" r:id="rId7"/>
+    <hyperlink ref="E74" r:id="rId8"/>
+    <hyperlink ref="P88" r:id="rId9"/>
+    <hyperlink ref="P87" r:id="rId10"/>
+    <hyperlink ref="P78" r:id="rId11"/>
+    <hyperlink ref="P74" r:id="rId12"/>
+    <hyperlink ref="G31" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="F23" r:id="rId15"/>
+    <hyperlink ref="F25" r:id="rId16"/>
+    <hyperlink ref="F29" r:id="rId17"/>
+    <hyperlink ref="F31" r:id="rId18"/>
+    <hyperlink ref="F33" r:id="rId19"/>
+    <hyperlink ref="F35" r:id="rId20"/>
+    <hyperlink ref="F37" r:id="rId21"/>
+    <hyperlink ref="P29" r:id="rId22"/>
+    <hyperlink ref="G27" r:id="rId23"/>
+    <hyperlink ref="G17" r:id="rId24"/>
+    <hyperlink ref="G33" r:id="rId25"/>
+    <hyperlink ref="G35" r:id="rId26"/>
+    <hyperlink ref="F96" r:id="rId27"/>
+    <hyperlink ref="P96" r:id="rId28"/>
+    <hyperlink ref="G93" r:id="rId29"/>
+    <hyperlink ref="G106" r:id="rId30"/>
+    <hyperlink ref="G108" r:id="rId31"/>
+    <hyperlink ref="G110" r:id="rId32"/>
+    <hyperlink ref="F168" r:id="rId33"/>
+    <hyperlink ref="P190" r:id="rId34"/>
+    <hyperlink ref="P192" r:id="rId35"/>
+    <hyperlink ref="F210" r:id="rId36"/>
+    <hyperlink ref="F19" r:id="rId37" location="scrollTo=5f2emlnJM56A"/>
+    <hyperlink ref="F220" r:id="rId38"/>
+    <hyperlink ref="P84" r:id="rId39"/>
+    <hyperlink ref="P233" r:id="rId40"/>
+    <hyperlink ref="P234" r:id="rId41"/>
+    <hyperlink ref="B33" r:id="rId42"/>
+    <hyperlink ref="F98" r:id="rId43"/>
+    <hyperlink ref="G98" r:id="rId44"/>
+    <hyperlink ref="F100" r:id="rId45"/>
+    <hyperlink ref="F123" r:id="rId46"/>
+    <hyperlink ref="F139" r:id="rId47"/>
+    <hyperlink ref="F102" r:id="rId48"/>
+    <hyperlink ref="G102" r:id="rId49"/>
+    <hyperlink ref="G104" r:id="rId50"/>
+    <hyperlink ref="F104" r:id="rId51"/>
+    <hyperlink ref="F106" r:id="rId52"/>
+    <hyperlink ref="F110" r:id="rId53"/>
+    <hyperlink ref="F112" r:id="rId54"/>
+    <hyperlink ref="F115" r:id="rId55"/>
+    <hyperlink ref="G115" r:id="rId56"/>
+    <hyperlink ref="F117" r:id="rId57"/>
+    <hyperlink ref="F11" r:id="rId58"/>
+    <hyperlink ref="B11" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId59"/>
+  <pageSetup orientation="portrait" r:id="rId60"/>
 </worksheet>
 </file>
 
@@ -3945,4 +4328,301 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E60"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="17" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>387</v>
+      </c>
+      <c r="B5" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>367</v>
+      </c>
+      <c r="D11" s="16"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>370</v>
+      </c>
+      <c r="B12" t="s">
+        <v>369</v>
+      </c>
+      <c r="D12" s="16"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>371</v>
+      </c>
+      <c r="B13" t="s">
+        <v>372</v>
+      </c>
+      <c r="D13" s="16"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>373</v>
+      </c>
+      <c r="B18" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>376</v>
+      </c>
+      <c r="B21" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>379</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>381</v>
+      </c>
+      <c r="B29" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>383</v>
+      </c>
+      <c r="B30" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="B46" s="3"/>
+    </row>
+    <row r="48" spans="1:2" s="17" customFormat="1">
+      <c r="A48" s="17" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="60.75">
+      <c r="A57" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="B57" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="B59" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>408</v>
+      </c>
+      <c r="C60" t="s">
+        <v>410</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A2:A13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" s="27" customFormat="1" ht="13.5">
+      <c r="A7" s="26" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" s="27" customFormat="1" ht="13.5">
+      <c r="A8" s="26" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" s="27" customFormat="1" ht="13.5">
+      <c r="A9" s="26" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" s="27" customFormat="1" ht="13.5">
+      <c r="A10" s="26" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" s="27" customFormat="1" ht="12.75"/>
+    <row r="12" spans="1:1" s="27" customFormat="1" ht="13.5">
+      <c r="A12" s="26" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" s="27" customFormat="1" ht="13.5">
+      <c r="A13" s="26" t="s">
+        <v>424</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>